--- a/output/yearly_population_iteration_75_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_75_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6543</v>
+        <v>5229</v>
       </c>
       <c r="C2" t="n">
-        <v>8103</v>
+        <v>8565</v>
       </c>
       <c r="D2" t="n">
-        <v>29160</v>
+        <v>42684</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4537</v>
+        <v>3401</v>
       </c>
       <c r="C3" t="n">
-        <v>5760</v>
+        <v>4667</v>
       </c>
       <c r="D3" t="n">
-        <v>10181</v>
+        <v>17712</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3386</v>
+        <v>2792</v>
       </c>
       <c r="C4" t="n">
-        <v>5022</v>
+        <v>4403</v>
       </c>
       <c r="D4" t="n">
-        <v>5129</v>
+        <v>8239</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2162</v>
+        <v>1781</v>
       </c>
       <c r="C5" t="n">
-        <v>3555</v>
+        <v>3917</v>
       </c>
       <c r="D5" t="n">
-        <v>2045</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1301</v>
+        <v>1009</v>
       </c>
       <c r="C6" t="n">
-        <v>2261</v>
+        <v>2773</v>
       </c>
       <c r="D6" t="n">
-        <v>963</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>636</v>
+        <v>482</v>
       </c>
       <c r="C7" t="n">
-        <v>1270</v>
+        <v>1341</v>
       </c>
       <c r="D7" t="n">
-        <v>637</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="C8" t="n">
-        <v>576</v>
+        <v>548</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
         <v>309</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8187</v>
+        <v>6156</v>
       </c>
       <c r="C2" t="n">
-        <v>12907</v>
+        <v>8660</v>
       </c>
       <c r="D2" t="n">
-        <v>28002</v>
+        <v>34592</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4467</v>
+        <v>3437</v>
       </c>
       <c r="C3" t="n">
-        <v>6025</v>
+        <v>5689</v>
       </c>
       <c r="D3" t="n">
-        <v>12213</v>
+        <v>19917</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3374</v>
+        <v>2620</v>
       </c>
       <c r="C4" t="n">
-        <v>5237</v>
+        <v>4440</v>
       </c>
       <c r="D4" t="n">
-        <v>5846</v>
+        <v>9455</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2390</v>
+        <v>1962</v>
       </c>
       <c r="C5" t="n">
-        <v>4199</v>
+        <v>4026</v>
       </c>
       <c r="D5" t="n">
-        <v>2466</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1540</v>
+        <v>1236</v>
       </c>
       <c r="C6" t="n">
-        <v>2824</v>
+        <v>3272</v>
       </c>
       <c r="D6" t="n">
-        <v>1126</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>845</v>
+        <v>634</v>
       </c>
       <c r="C7" t="n">
-        <v>1735</v>
+        <v>1972</v>
       </c>
       <c r="D7" t="n">
-        <v>675</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>361</v>
+        <v>271</v>
       </c>
       <c r="C8" t="n">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
-        <v>421</v>
+        <v>387</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10101</v>
+        <v>9251</v>
       </c>
       <c r="C2" t="n">
-        <v>11281</v>
+        <v>9372</v>
       </c>
       <c r="D2" t="n">
-        <v>28631</v>
+        <v>39989</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4903</v>
+        <v>3706</v>
       </c>
       <c r="C3" t="n">
-        <v>7963</v>
+        <v>6150</v>
       </c>
       <c r="D3" t="n">
-        <v>13432</v>
+        <v>20488</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3275</v>
+        <v>2526</v>
       </c>
       <c r="C4" t="n">
-        <v>5440</v>
+        <v>4911</v>
       </c>
       <c r="D4" t="n">
-        <v>6590</v>
+        <v>10774</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2512</v>
+        <v>2008</v>
       </c>
       <c r="C5" t="n">
-        <v>4580</v>
+        <v>4082</v>
       </c>
       <c r="D5" t="n">
-        <v>2910</v>
+        <v>4482</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1727</v>
+        <v>1394</v>
       </c>
       <c r="C6" t="n">
-        <v>3363</v>
+        <v>3560</v>
       </c>
       <c r="D6" t="n">
-        <v>1293</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1019</v>
+        <v>786</v>
       </c>
       <c r="C7" t="n">
-        <v>2203</v>
+        <v>2486</v>
       </c>
       <c r="D7" t="n">
-        <v>734</v>
+        <v>824</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>493</v>
+        <v>366</v>
       </c>
       <c r="C8" t="n">
-        <v>1224</v>
+        <v>1319</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="C9" t="n">
-        <v>606</v>
+        <v>586</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
         <v>209</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9097</v>
+        <v>8199</v>
       </c>
       <c r="C2" t="n">
-        <v>7490</v>
+        <v>6297</v>
       </c>
       <c r="D2" t="n">
-        <v>23191</v>
+        <v>32777</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5965</v>
+        <v>4520</v>
       </c>
       <c r="C3" t="n">
-        <v>11267</v>
+        <v>9083</v>
       </c>
       <c r="D3" t="n">
-        <v>14569</v>
+        <v>22088</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2321</v>
+        <v>1855</v>
       </c>
       <c r="C4" t="n">
-        <v>7530</v>
+        <v>6653</v>
       </c>
       <c r="D4" t="n">
-        <v>6348</v>
+        <v>10191</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1595</v>
+        <v>1288</v>
       </c>
       <c r="C5" t="n">
-        <v>3295</v>
+        <v>3488</v>
       </c>
       <c r="D5" t="n">
-        <v>2077</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>941</v>
+        <v>726</v>
       </c>
       <c r="C6" t="n">
-        <v>2158</v>
+        <v>2436</v>
       </c>
       <c r="D6" t="n">
-        <v>719</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>455</v>
+        <v>338</v>
       </c>
       <c r="C7" t="n">
-        <v>1199</v>
+        <v>1292</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>135</v>
       </c>
       <c r="C8" t="n">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
         <v>204</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5608</v>
+        <v>4760</v>
       </c>
       <c r="C2" t="n">
-        <v>3940</v>
+        <v>3448</v>
       </c>
       <c r="D2" t="n">
-        <v>17537</v>
+        <v>22751</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6309</v>
+        <v>5192</v>
       </c>
       <c r="C3" t="n">
-        <v>8583</v>
+        <v>7066</v>
       </c>
       <c r="D3" t="n">
-        <v>15087</v>
+        <v>22269</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3273</v>
+        <v>2517</v>
       </c>
       <c r="C4" t="n">
-        <v>9384</v>
+        <v>7913</v>
       </c>
       <c r="D4" t="n">
-        <v>7478</v>
+        <v>11904</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1786</v>
+        <v>1434</v>
       </c>
       <c r="C5" t="n">
-        <v>5214</v>
+        <v>4855</v>
       </c>
       <c r="D5" t="n">
-        <v>2647</v>
+        <v>3869</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1132</v>
+        <v>871</v>
       </c>
       <c r="C6" t="n">
-        <v>2703</v>
+        <v>2957</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>431</v>
+        <v>319</v>
       </c>
       <c r="C7" t="n">
-        <v>1565</v>
+        <v>1719</v>
       </c>
       <c r="D7" t="n">
-        <v>508</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>793</v>
+        <v>774</v>
       </c>
       <c r="D8" t="n">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6736</v>
+        <v>4754</v>
       </c>
       <c r="C2" t="n">
-        <v>7391</v>
+        <v>6914</v>
       </c>
       <c r="D2" t="n">
-        <v>21972</v>
+        <v>27549</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5037</v>
+        <v>4203</v>
       </c>
       <c r="C3" t="n">
-        <v>5574</v>
+        <v>4690</v>
       </c>
       <c r="D3" t="n">
-        <v>14401</v>
+        <v>21020</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3984</v>
+        <v>3166</v>
       </c>
       <c r="C4" t="n">
-        <v>8781</v>
+        <v>7325</v>
       </c>
       <c r="D4" t="n">
-        <v>8565</v>
+        <v>13119</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2155</v>
+        <v>1684</v>
       </c>
       <c r="C5" t="n">
-        <v>7197</v>
+        <v>6268</v>
       </c>
       <c r="D5" t="n">
-        <v>3354</v>
+        <v>5062</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1300</v>
+        <v>1016</v>
       </c>
       <c r="C6" t="n">
-        <v>3833</v>
+        <v>3784</v>
       </c>
       <c r="D6" t="n">
-        <v>1123</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>634</v>
+        <v>474</v>
       </c>
       <c r="C7" t="n">
-        <v>2092</v>
+        <v>2281</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>219</v>
+        <v>163</v>
       </c>
       <c r="C8" t="n">
-        <v>1125</v>
+        <v>1170</v>
       </c>
       <c r="D8" t="n">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>537</v>
+        <v>507</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="D10" t="n">
         <v>216</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3975</v>
+        <v>2822</v>
       </c>
       <c r="C2" t="n">
-        <v>3333</v>
+        <v>3169</v>
       </c>
       <c r="D2" t="n">
-        <v>15128</v>
+        <v>19013</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5264</v>
+        <v>4182</v>
       </c>
       <c r="C3" t="n">
-        <v>6026</v>
+        <v>5304</v>
       </c>
       <c r="D3" t="n">
-        <v>14903</v>
+        <v>21246</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4416</v>
+        <v>3509</v>
       </c>
       <c r="C4" t="n">
-        <v>8417</v>
+        <v>7060</v>
       </c>
       <c r="D4" t="n">
-        <v>9275</v>
+        <v>14282</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2273</v>
+        <v>1770</v>
       </c>
       <c r="C5" t="n">
-        <v>8514</v>
+        <v>7388</v>
       </c>
       <c r="D5" t="n">
-        <v>3658</v>
+        <v>5345</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1126</v>
+        <v>851</v>
       </c>
       <c r="C6" t="n">
-        <v>4725</v>
+        <v>4599</v>
       </c>
       <c r="D6" t="n">
-        <v>1120</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>2164</v>
+        <v>2299</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>879</v>
+        <v>863</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5914</v>
+        <v>3519</v>
       </c>
       <c r="C2" t="n">
-        <v>9537</v>
+        <v>5742</v>
       </c>
       <c r="D2" t="n">
-        <v>13622</v>
+        <v>23323</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4026</v>
+        <v>3099</v>
       </c>
       <c r="C3" t="n">
-        <v>4252</v>
+        <v>3864</v>
       </c>
       <c r="D3" t="n">
-        <v>13932</v>
+        <v>19514</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4164</v>
+        <v>3302</v>
       </c>
       <c r="C4" t="n">
-        <v>7094</v>
+        <v>6087</v>
       </c>
       <c r="D4" t="n">
-        <v>9911</v>
+        <v>15121</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2799</v>
+        <v>2188</v>
       </c>
       <c r="C5" t="n">
-        <v>8373</v>
+        <v>7157</v>
       </c>
       <c r="D5" t="n">
-        <v>4409</v>
+        <v>6469</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1442</v>
+        <v>1097</v>
       </c>
       <c r="C6" t="n">
-        <v>6363</v>
+        <v>5779</v>
       </c>
       <c r="D6" t="n">
-        <v>1481</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>436</v>
+        <v>320</v>
       </c>
       <c r="C7" t="n">
-        <v>3259</v>
+        <v>3267</v>
       </c>
       <c r="D7" t="n">
-        <v>630</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>1374</v>
+        <v>1400</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>46</v>
+      </c>
+      <c r="D14" t="n">
         <v>47</v>
-      </c>
-      <c r="D14" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3963</v>
+        <v>2403</v>
       </c>
       <c r="C2" t="n">
-        <v>4942</v>
+        <v>3035</v>
       </c>
       <c r="D2" t="n">
-        <v>10229</v>
+        <v>16974</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4070</v>
+        <v>2833</v>
       </c>
       <c r="C3" t="n">
-        <v>5836</v>
+        <v>4218</v>
       </c>
       <c r="D3" t="n">
-        <v>13136</v>
+        <v>18909</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3795</v>
+        <v>2958</v>
       </c>
       <c r="C4" t="n">
-        <v>5977</v>
+        <v>5180</v>
       </c>
       <c r="D4" t="n">
-        <v>10245</v>
+        <v>15396</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3066</v>
+        <v>2405</v>
       </c>
       <c r="C5" t="n">
-        <v>7973</v>
+        <v>6892</v>
       </c>
       <c r="D5" t="n">
-        <v>4993</v>
+        <v>7393</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1683</v>
+        <v>1289</v>
       </c>
       <c r="C6" t="n">
-        <v>7329</v>
+        <v>6446</v>
       </c>
       <c r="D6" t="n">
-        <v>1745</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>4209</v>
+        <v>4105</v>
       </c>
       <c r="D7" t="n">
-        <v>706</v>
+        <v>803</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="D8" t="n">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6019</v>
+        <v>4375</v>
       </c>
       <c r="C2" t="n">
-        <v>4752</v>
+        <v>8726</v>
       </c>
       <c r="D2" t="n">
-        <v>14060</v>
+        <v>27684</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3392</v>
+        <v>2256</v>
       </c>
       <c r="C3" t="n">
-        <v>4860</v>
+        <v>3360</v>
       </c>
       <c r="D3" t="n">
-        <v>11946</v>
+        <v>17466</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3382</v>
+        <v>2532</v>
       </c>
       <c r="C4" t="n">
-        <v>5791</v>
+        <v>4665</v>
       </c>
       <c r="D4" t="n">
-        <v>10349</v>
+        <v>15433</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3054</v>
+        <v>2390</v>
       </c>
       <c r="C5" t="n">
-        <v>6983</v>
+        <v>6058</v>
       </c>
       <c r="D5" t="n">
-        <v>5499</v>
+        <v>8243</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1982</v>
+        <v>1546</v>
       </c>
       <c r="C6" t="n">
-        <v>7519</v>
+        <v>6563</v>
       </c>
       <c r="D6" t="n">
-        <v>2158</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>730</v>
+        <v>541</v>
       </c>
       <c r="C7" t="n">
-        <v>5441</v>
+        <v>4975</v>
       </c>
       <c r="D7" t="n">
-        <v>831</v>
+        <v>966</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>2675</v>
+        <v>2655</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>993</v>
+        <v>963</v>
       </c>
       <c r="D9" t="n">
-        <v>314</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
         <v>65</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7181</v>
+        <v>5343</v>
       </c>
       <c r="C2" t="n">
-        <v>3590</v>
+        <v>3006</v>
       </c>
       <c r="D2" t="n">
-        <v>4183</v>
+        <v>5317</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4307</v>
+        <v>3128</v>
       </c>
       <c r="C2" t="n">
-        <v>2699</v>
+        <v>5026</v>
       </c>
       <c r="D2" t="n">
-        <v>10349</v>
+        <v>20375</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4485</v>
+        <v>3126</v>
       </c>
       <c r="C3" t="n">
-        <v>5254</v>
+        <v>4857</v>
       </c>
       <c r="D3" t="n">
-        <v>13063</v>
+        <v>19576</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4552</v>
+        <v>3479</v>
       </c>
       <c r="C4" t="n">
-        <v>8217</v>
+        <v>6720</v>
       </c>
       <c r="D4" t="n">
-        <v>10559</v>
+        <v>15756</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1916</v>
+        <v>1494</v>
       </c>
       <c r="C5" t="n">
-        <v>10453</v>
+        <v>9041</v>
       </c>
       <c r="D5" t="n">
-        <v>5016</v>
+        <v>7371</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>674</v>
+        <v>499</v>
       </c>
       <c r="C6" t="n">
-        <v>6805</v>
+        <v>6161</v>
       </c>
       <c r="D6" t="n">
-        <v>1765</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>2621</v>
+        <v>2601</v>
       </c>
       <c r="D7" t="n">
-        <v>547</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>973</v>
+        <v>943</v>
       </c>
       <c r="D8" t="n">
-        <v>307</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
         <v>63</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8400</v>
+        <v>6622</v>
       </c>
       <c r="C2" t="n">
-        <v>3633</v>
+        <v>3439</v>
       </c>
       <c r="D2" t="n">
-        <v>6181</v>
+        <v>20169</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3050</v>
+        <v>2271</v>
       </c>
       <c r="C3" t="n">
-        <v>1838</v>
+        <v>1539</v>
       </c>
       <c r="D3" t="n">
-        <v>1375</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5513</v>
+        <v>4527</v>
       </c>
       <c r="C2" t="n">
-        <v>4067</v>
+        <v>6602</v>
       </c>
       <c r="D2" t="n">
-        <v>11636</v>
+        <v>24516</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4767</v>
+        <v>3649</v>
       </c>
       <c r="C3" t="n">
-        <v>2472</v>
+        <v>2267</v>
       </c>
       <c r="D3" t="n">
-        <v>2081</v>
+        <v>4582</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1358</v>
+        <v>1020</v>
       </c>
       <c r="C4" t="n">
-        <v>1137</v>
+        <v>959</v>
       </c>
       <c r="D4" t="n">
-        <v>1458</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="5">
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
         <v>441</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4994,7 +4994,7 @@
         <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5008,7 +5008,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6333</v>
+        <v>4988</v>
       </c>
       <c r="C2" t="n">
-        <v>7230</v>
+        <v>8246</v>
       </c>
       <c r="D2" t="n">
-        <v>22737</v>
+        <v>36238</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4235</v>
+        <v>3396</v>
       </c>
       <c r="C3" t="n">
-        <v>2901</v>
+        <v>4008</v>
       </c>
       <c r="D3" t="n">
-        <v>3459</v>
+        <v>7441</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2632</v>
+        <v>1975</v>
       </c>
       <c r="C4" t="n">
-        <v>1882</v>
+        <v>1670</v>
       </c>
       <c r="D4" t="n">
-        <v>1519</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>616</v>
+        <v>479</v>
       </c>
       <c r="C5" t="n">
-        <v>726</v>
+        <v>626</v>
       </c>
       <c r="D5" t="n">
-        <v>1202</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
         <v>303</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>625</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
         <v>462</v>
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5277,7 +5277,7 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>211</v>
@@ -5291,7 +5291,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>121</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5851</v>
+        <v>5634</v>
       </c>
       <c r="C2" t="n">
-        <v>4428</v>
+        <v>7304</v>
       </c>
       <c r="D2" t="n">
-        <v>22436</v>
+        <v>27159</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4344</v>
+        <v>3408</v>
       </c>
       <c r="C3" t="n">
-        <v>4494</v>
+        <v>5414</v>
       </c>
       <c r="D3" t="n">
-        <v>6145</v>
+        <v>11294</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2906</v>
+        <v>2268</v>
       </c>
       <c r="C4" t="n">
-        <v>2400</v>
+        <v>2914</v>
       </c>
       <c r="D4" t="n">
-        <v>1812</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1344</v>
+        <v>1021</v>
       </c>
       <c r="C5" t="n">
-        <v>1314</v>
+        <v>1164</v>
       </c>
       <c r="D5" t="n">
-        <v>1223</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>333</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>518</v>
+        <v>461</v>
       </c>
       <c r="D6" t="n">
-        <v>938</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5588,7 +5588,7 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
         <v>218</v>
@@ -5602,7 +5602,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5613,7 +5613,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>100</v>
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7284</v>
+        <v>5858</v>
       </c>
       <c r="C2" t="n">
-        <v>7797</v>
+        <v>4939</v>
       </c>
       <c r="D2" t="n">
-        <v>17535</v>
+        <v>27707</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3712</v>
+        <v>3281</v>
       </c>
       <c r="C3" t="n">
-        <v>3650</v>
+        <v>5237</v>
       </c>
       <c r="D3" t="n">
-        <v>7703</v>
+        <v>12146</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2249</v>
+        <v>1773</v>
       </c>
       <c r="C4" t="n">
-        <v>2914</v>
+        <v>3540</v>
       </c>
       <c r="D4" t="n">
-        <v>2208</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1126</v>
+        <v>857</v>
       </c>
       <c r="C5" t="n">
-        <v>1389</v>
+        <v>1522</v>
       </c>
       <c r="D5" t="n">
-        <v>1048</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>397</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>625</v>
+        <v>554</v>
       </c>
       <c r="D6" t="n">
-        <v>743</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>149</v>
@@ -5913,7 +5913,7 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5986,7 +5986,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7069</v>
+        <v>5906</v>
       </c>
       <c r="C2" t="n">
-        <v>7646</v>
+        <v>6387</v>
       </c>
       <c r="D2" t="n">
-        <v>17805</v>
+        <v>30094</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4659</v>
+        <v>3844</v>
       </c>
       <c r="C3" t="n">
-        <v>5280</v>
+        <v>4338</v>
       </c>
       <c r="D3" t="n">
-        <v>8854</v>
+        <v>13971</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2608</v>
+        <v>2206</v>
       </c>
       <c r="C4" t="n">
-        <v>3312</v>
+        <v>4509</v>
       </c>
       <c r="D4" t="n">
-        <v>3301</v>
+        <v>5447</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1525</v>
+        <v>1181</v>
       </c>
       <c r="C5" t="n">
-        <v>2282</v>
+        <v>2691</v>
       </c>
       <c r="D5" t="n">
-        <v>1239</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>717</v>
+        <v>540</v>
       </c>
       <c r="C6" t="n">
-        <v>1058</v>
+        <v>1104</v>
       </c>
       <c r="D6" t="n">
-        <v>793</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>229</v>
+        <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>481</v>
+        <v>424</v>
       </c>
       <c r="D7" t="n">
         <v>561</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6185,7 +6185,7 @@
         <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6138</v>
+        <v>4244</v>
       </c>
       <c r="C2" t="n">
-        <v>7466</v>
+        <v>5963</v>
       </c>
       <c r="D2" t="n">
-        <v>17329</v>
+        <v>37011</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4829</v>
+        <v>3999</v>
       </c>
       <c r="C3" t="n">
-        <v>5708</v>
+        <v>4731</v>
       </c>
       <c r="D3" t="n">
-        <v>9706</v>
+        <v>15544</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3157</v>
+        <v>2614</v>
       </c>
       <c r="C4" t="n">
-        <v>4395</v>
+        <v>4316</v>
       </c>
       <c r="D4" t="n">
-        <v>4320</v>
+        <v>6865</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1821</v>
+        <v>1480</v>
       </c>
       <c r="C5" t="n">
-        <v>2796</v>
+        <v>3647</v>
       </c>
       <c r="D5" t="n">
-        <v>1597</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1034</v>
+        <v>787</v>
       </c>
       <c r="C6" t="n">
-        <v>1726</v>
+        <v>1944</v>
       </c>
       <c r="D6" t="n">
-        <v>855</v>
+        <v>992</v>
       </c>
     </row>
     <row r="7">
@@ -6448,10 +6448,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>319</v>
       </c>
       <c r="C7" t="n">
-        <v>797</v>
+        <v>779</v>
       </c>
       <c r="D7" t="n">
         <v>598</v>
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>373</v>
+        <v>336</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_75_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_75_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5229</v>
+        <v>7236</v>
       </c>
       <c r="C2" t="n">
-        <v>8565</v>
+        <v>10199</v>
       </c>
       <c r="D2" t="n">
-        <v>42684</v>
+        <v>27474</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3401</v>
+        <v>4301</v>
       </c>
       <c r="C3" t="n">
-        <v>4667</v>
+        <v>3899</v>
       </c>
       <c r="D3" t="n">
-        <v>17712</v>
+        <v>16528</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2792</v>
+        <v>3399</v>
       </c>
       <c r="C4" t="n">
-        <v>4403</v>
+        <v>4265</v>
       </c>
       <c r="D4" t="n">
-        <v>8239</v>
+        <v>8704</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1781</v>
+        <v>2203</v>
       </c>
       <c r="C5" t="n">
-        <v>3917</v>
+        <v>3875</v>
       </c>
       <c r="D5" t="n">
-        <v>3076</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1009</v>
+        <v>1234</v>
       </c>
       <c r="C6" t="n">
-        <v>2773</v>
+        <v>2818</v>
       </c>
       <c r="D6" t="n">
-        <v>1221</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>482</v>
+        <v>593</v>
       </c>
       <c r="C7" t="n">
-        <v>1341</v>
+        <v>1516</v>
       </c>
       <c r="D7" t="n">
-        <v>657</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="C8" t="n">
-        <v>548</v>
+        <v>641</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6156</v>
+        <v>8476</v>
       </c>
       <c r="C2" t="n">
-        <v>8660</v>
+        <v>9849</v>
       </c>
       <c r="D2" t="n">
-        <v>34592</v>
+        <v>31736</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3437</v>
+        <v>4593</v>
       </c>
       <c r="C3" t="n">
-        <v>5689</v>
+        <v>5951</v>
       </c>
       <c r="D3" t="n">
-        <v>19917</v>
+        <v>16905</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2620</v>
+        <v>3239</v>
       </c>
       <c r="C4" t="n">
-        <v>4440</v>
+        <v>4000</v>
       </c>
       <c r="D4" t="n">
-        <v>9455</v>
+        <v>9716</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1962</v>
+        <v>2400</v>
       </c>
       <c r="C5" t="n">
-        <v>4026</v>
+        <v>3936</v>
       </c>
       <c r="D5" t="n">
-        <v>3825</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1236</v>
+        <v>1500</v>
       </c>
       <c r="C6" t="n">
-        <v>3272</v>
+        <v>3267</v>
       </c>
       <c r="D6" t="n">
-        <v>1477</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>634</v>
+        <v>783</v>
       </c>
       <c r="C7" t="n">
-        <v>1972</v>
+        <v>2074</v>
       </c>
       <c r="D7" t="n">
-        <v>738</v>
+        <v>776</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>271</v>
+        <v>326</v>
       </c>
       <c r="C8" t="n">
-        <v>897</v>
+        <v>1018</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C9" t="n">
-        <v>387</v>
+        <v>428</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
         <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9251</v>
+        <v>9488</v>
       </c>
       <c r="C2" t="n">
-        <v>9372</v>
+        <v>13807</v>
       </c>
       <c r="D2" t="n">
-        <v>39989</v>
+        <v>38175</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3706</v>
+        <v>5002</v>
       </c>
       <c r="C3" t="n">
-        <v>6150</v>
+        <v>6766</v>
       </c>
       <c r="D3" t="n">
-        <v>20488</v>
+        <v>17602</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2526</v>
+        <v>3225</v>
       </c>
       <c r="C4" t="n">
-        <v>4911</v>
+        <v>4721</v>
       </c>
       <c r="D4" t="n">
-        <v>10774</v>
+        <v>10362</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2008</v>
+        <v>2462</v>
       </c>
       <c r="C5" t="n">
-        <v>4082</v>
+        <v>3843</v>
       </c>
       <c r="D5" t="n">
-        <v>4482</v>
+        <v>4782</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1394</v>
+        <v>1690</v>
       </c>
       <c r="C6" t="n">
-        <v>3560</v>
+        <v>3513</v>
       </c>
       <c r="D6" t="n">
-        <v>1795</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>786</v>
+        <v>955</v>
       </c>
       <c r="C7" t="n">
-        <v>2486</v>
+        <v>2532</v>
       </c>
       <c r="D7" t="n">
-        <v>824</v>
+        <v>882</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>366</v>
+        <v>443</v>
       </c>
       <c r="C8" t="n">
-        <v>1319</v>
+        <v>1421</v>
       </c>
       <c r="D8" t="n">
-        <v>491</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C9" t="n">
-        <v>586</v>
+        <v>653</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
         <v>256</v>
@@ -1531,10 +1531,10 @@
         <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1618,7 +1618,7 @@
         <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8199</v>
+        <v>8710</v>
       </c>
       <c r="C2" t="n">
-        <v>6297</v>
+        <v>9388</v>
       </c>
       <c r="D2" t="n">
-        <v>32777</v>
+        <v>31384</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4520</v>
+        <v>5901</v>
       </c>
       <c r="C3" t="n">
-        <v>9083</v>
+        <v>10101</v>
       </c>
       <c r="D3" t="n">
-        <v>22088</v>
+        <v>19236</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1855</v>
+        <v>2274</v>
       </c>
       <c r="C4" t="n">
-        <v>6653</v>
+        <v>6272</v>
       </c>
       <c r="D4" t="n">
-        <v>10191</v>
+        <v>10069</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1288</v>
+        <v>1561</v>
       </c>
       <c r="C5" t="n">
-        <v>3488</v>
+        <v>3442</v>
       </c>
       <c r="D5" t="n">
-        <v>3006</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>726</v>
+        <v>882</v>
       </c>
       <c r="C6" t="n">
-        <v>2436</v>
+        <v>2481</v>
       </c>
       <c r="D6" t="n">
-        <v>807</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>409</v>
       </c>
       <c r="C7" t="n">
-        <v>1292</v>
+        <v>1392</v>
       </c>
       <c r="D7" t="n">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>574</v>
+        <v>639</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
         <v>250</v>
@@ -1828,10 +1828,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
@@ -1915,7 +1915,7 @@
         <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4760</v>
+        <v>5407</v>
       </c>
       <c r="C2" t="n">
-        <v>3448</v>
+        <v>4517</v>
       </c>
       <c r="D2" t="n">
-        <v>22751</v>
+        <v>21887</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5192</v>
+        <v>6105</v>
       </c>
       <c r="C3" t="n">
-        <v>7066</v>
+        <v>8872</v>
       </c>
       <c r="D3" t="n">
-        <v>22269</v>
+        <v>19780</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2517</v>
+        <v>3162</v>
       </c>
       <c r="C4" t="n">
-        <v>7913</v>
+        <v>8086</v>
       </c>
       <c r="D4" t="n">
-        <v>11904</v>
+        <v>11364</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1434</v>
+        <v>1739</v>
       </c>
       <c r="C5" t="n">
-        <v>4855</v>
+        <v>4703</v>
       </c>
       <c r="D5" t="n">
-        <v>3869</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>871</v>
+        <v>1044</v>
       </c>
       <c r="C6" t="n">
-        <v>2957</v>
+        <v>2964</v>
       </c>
       <c r="D6" t="n">
-        <v>1031</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>385</v>
       </c>
       <c r="C7" t="n">
-        <v>1719</v>
+        <v>1788</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>774</v>
+        <v>862</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
         <v>96</v>
@@ -2212,7 +2212,7 @@
         <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4754</v>
+        <v>5160</v>
       </c>
       <c r="C2" t="n">
-        <v>6914</v>
+        <v>8125</v>
       </c>
       <c r="D2" t="n">
-        <v>27549</v>
+        <v>27219</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4203</v>
+        <v>4928</v>
       </c>
       <c r="C3" t="n">
-        <v>4690</v>
+        <v>6052</v>
       </c>
       <c r="D3" t="n">
-        <v>21020</v>
+        <v>18737</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3166</v>
+        <v>3775</v>
       </c>
       <c r="C4" t="n">
-        <v>7325</v>
+        <v>8302</v>
       </c>
       <c r="D4" t="n">
-        <v>13119</v>
+        <v>12392</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1684</v>
+        <v>2079</v>
       </c>
       <c r="C5" t="n">
-        <v>6268</v>
+        <v>6196</v>
       </c>
       <c r="D5" t="n">
-        <v>5062</v>
+        <v>5059</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1016</v>
+        <v>1234</v>
       </c>
       <c r="C6" t="n">
-        <v>3784</v>
+        <v>3748</v>
       </c>
       <c r="D6" t="n">
-        <v>1453</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>474</v>
+        <v>561</v>
       </c>
       <c r="C7" t="n">
-        <v>2281</v>
+        <v>2311</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="C8" t="n">
-        <v>1170</v>
+        <v>1242</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>507</v>
+        <v>535</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2822</v>
+        <v>3093</v>
       </c>
       <c r="C2" t="n">
-        <v>3169</v>
+        <v>3827</v>
       </c>
       <c r="D2" t="n">
-        <v>19013</v>
+        <v>18988</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4182</v>
+        <v>4849</v>
       </c>
       <c r="C3" t="n">
-        <v>5304</v>
+        <v>6564</v>
       </c>
       <c r="D3" t="n">
-        <v>21246</v>
+        <v>19199</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3509</v>
+        <v>4146</v>
       </c>
       <c r="C4" t="n">
-        <v>7060</v>
+        <v>8191</v>
       </c>
       <c r="D4" t="n">
-        <v>14282</v>
+        <v>13206</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1770</v>
+        <v>2175</v>
       </c>
       <c r="C5" t="n">
-        <v>7388</v>
+        <v>7624</v>
       </c>
       <c r="D5" t="n">
-        <v>5345</v>
+        <v>5328</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>851</v>
+        <v>1020</v>
       </c>
       <c r="C6" t="n">
-        <v>4599</v>
+        <v>4497</v>
       </c>
       <c r="D6" t="n">
-        <v>1414</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>2299</v>
+        <v>2357</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>863</v>
+        <v>901</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
         <v>97</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3519</v>
+        <v>4482</v>
       </c>
       <c r="C2" t="n">
-        <v>5742</v>
+        <v>8143</v>
       </c>
       <c r="D2" t="n">
-        <v>23323</v>
+        <v>16803</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3099</v>
+        <v>3534</v>
       </c>
       <c r="C3" t="n">
-        <v>3864</v>
+        <v>4744</v>
       </c>
       <c r="D3" t="n">
-        <v>19514</v>
+        <v>18064</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3302</v>
+        <v>3907</v>
       </c>
       <c r="C4" t="n">
-        <v>6087</v>
+        <v>7333</v>
       </c>
       <c r="D4" t="n">
-        <v>15121</v>
+        <v>13725</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2188</v>
+        <v>2623</v>
       </c>
       <c r="C5" t="n">
-        <v>7157</v>
+        <v>7788</v>
       </c>
       <c r="D5" t="n">
-        <v>6469</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1097</v>
+        <v>1311</v>
       </c>
       <c r="C6" t="n">
-        <v>5779</v>
+        <v>5791</v>
       </c>
       <c r="D6" t="n">
-        <v>1923</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>320</v>
+        <v>384</v>
       </c>
       <c r="C7" t="n">
-        <v>3267</v>
+        <v>3218</v>
       </c>
       <c r="D7" t="n">
-        <v>699</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1400</v>
+        <v>1455</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2403</v>
+        <v>3168</v>
       </c>
       <c r="C2" t="n">
-        <v>3035</v>
+        <v>4898</v>
       </c>
       <c r="D2" t="n">
-        <v>16974</v>
+        <v>12855</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2833</v>
+        <v>3362</v>
       </c>
       <c r="C3" t="n">
-        <v>4218</v>
+        <v>5507</v>
       </c>
       <c r="D3" t="n">
-        <v>18909</v>
+        <v>17103</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2958</v>
+        <v>3499</v>
       </c>
       <c r="C4" t="n">
-        <v>5180</v>
+        <v>6347</v>
       </c>
       <c r="D4" t="n">
-        <v>15396</v>
+        <v>13981</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2405</v>
+        <v>2865</v>
       </c>
       <c r="C5" t="n">
-        <v>6892</v>
+        <v>7763</v>
       </c>
       <c r="D5" t="n">
-        <v>7393</v>
+        <v>6953</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1289</v>
+        <v>1530</v>
       </c>
       <c r="C6" t="n">
-        <v>6446</v>
+        <v>6630</v>
       </c>
       <c r="D6" t="n">
-        <v>2330</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>346</v>
       </c>
       <c r="C7" t="n">
-        <v>4105</v>
+        <v>4042</v>
       </c>
       <c r="D7" t="n">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1838</v>
+        <v>1864</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4375</v>
+        <v>3920</v>
       </c>
       <c r="C2" t="n">
-        <v>8726</v>
+        <v>11431</v>
       </c>
       <c r="D2" t="n">
-        <v>27684</v>
+        <v>13117</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2256</v>
+        <v>2774</v>
       </c>
       <c r="C3" t="n">
-        <v>3360</v>
+        <v>4737</v>
       </c>
       <c r="D3" t="n">
-        <v>17466</v>
+        <v>15498</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2532</v>
+        <v>2999</v>
       </c>
       <c r="C4" t="n">
-        <v>4665</v>
+        <v>5807</v>
       </c>
       <c r="D4" t="n">
-        <v>15433</v>
+        <v>14005</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2390</v>
+        <v>2836</v>
       </c>
       <c r="C5" t="n">
-        <v>6058</v>
+        <v>7030</v>
       </c>
       <c r="D5" t="n">
-        <v>8243</v>
+        <v>7686</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1546</v>
+        <v>1812</v>
       </c>
       <c r="C6" t="n">
-        <v>6563</v>
+        <v>7074</v>
       </c>
       <c r="D6" t="n">
-        <v>2932</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>541</v>
+        <v>635</v>
       </c>
       <c r="C7" t="n">
-        <v>4975</v>
+        <v>4978</v>
       </c>
       <c r="D7" t="n">
-        <v>966</v>
+        <v>977</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>2655</v>
+        <v>2610</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5343</v>
+        <v>7435</v>
       </c>
       <c r="C2" t="n">
-        <v>3006</v>
+        <v>2493</v>
       </c>
       <c r="D2" t="n">
-        <v>5317</v>
+        <v>16429</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3128</v>
+        <v>2839</v>
       </c>
       <c r="C2" t="n">
-        <v>5026</v>
+        <v>6584</v>
       </c>
       <c r="D2" t="n">
-        <v>20375</v>
+        <v>9759</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3126</v>
+        <v>3648</v>
       </c>
       <c r="C3" t="n">
-        <v>4857</v>
+        <v>6653</v>
       </c>
       <c r="D3" t="n">
-        <v>19576</v>
+        <v>16553</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3479</v>
+        <v>4152</v>
       </c>
       <c r="C4" t="n">
-        <v>6720</v>
+        <v>8256</v>
       </c>
       <c r="D4" t="n">
-        <v>15756</v>
+        <v>14348</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1494</v>
+        <v>1726</v>
       </c>
       <c r="C5" t="n">
-        <v>9041</v>
+        <v>10137</v>
       </c>
       <c r="D5" t="n">
-        <v>7371</v>
+        <v>6964</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>499</v>
+        <v>586</v>
       </c>
       <c r="C6" t="n">
-        <v>6161</v>
+        <v>6195</v>
       </c>
       <c r="D6" t="n">
-        <v>2260</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>2601</v>
+        <v>2557</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6622</v>
+        <v>8125</v>
       </c>
       <c r="C2" t="n">
-        <v>3439</v>
+        <v>7814</v>
       </c>
       <c r="D2" t="n">
-        <v>20169</v>
+        <v>24844</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2271</v>
+        <v>3158</v>
       </c>
       <c r="C3" t="n">
-        <v>1539</v>
+        <v>1256</v>
       </c>
       <c r="D3" t="n">
-        <v>1575</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4527</v>
+        <v>6330</v>
       </c>
       <c r="C2" t="n">
-        <v>6602</v>
+        <v>5588</v>
       </c>
       <c r="D2" t="n">
-        <v>24516</v>
+        <v>30724</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3649</v>
+        <v>4633</v>
       </c>
       <c r="C3" t="n">
-        <v>2267</v>
+        <v>4283</v>
       </c>
       <c r="D3" t="n">
-        <v>4582</v>
+        <v>6751</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1020</v>
+        <v>1406</v>
       </c>
       <c r="C4" t="n">
-        <v>959</v>
+        <v>781</v>
       </c>
       <c r="D4" t="n">
-        <v>1498</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4988</v>
+        <v>5235</v>
       </c>
       <c r="C2" t="n">
-        <v>8246</v>
+        <v>7334</v>
       </c>
       <c r="D2" t="n">
-        <v>36238</v>
+        <v>29635</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3396</v>
+        <v>4494</v>
       </c>
       <c r="C3" t="n">
-        <v>4008</v>
+        <v>4323</v>
       </c>
       <c r="D3" t="n">
-        <v>7441</v>
+        <v>10100</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1975</v>
+        <v>2569</v>
       </c>
       <c r="C4" t="n">
-        <v>1670</v>
+        <v>2748</v>
       </c>
       <c r="D4" t="n">
-        <v>2044</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>479</v>
+        <v>625</v>
       </c>
       <c r="C5" t="n">
-        <v>626</v>
+        <v>523</v>
       </c>
       <c r="D5" t="n">
-        <v>1195</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5634</v>
+        <v>7266</v>
       </c>
       <c r="C2" t="n">
-        <v>7304</v>
+        <v>6570</v>
       </c>
       <c r="D2" t="n">
-        <v>27159</v>
+        <v>22373</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3408</v>
+        <v>3994</v>
       </c>
       <c r="C3" t="n">
-        <v>5414</v>
+        <v>5111</v>
       </c>
       <c r="D3" t="n">
-        <v>11294</v>
+        <v>12358</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2268</v>
+        <v>2965</v>
       </c>
       <c r="C4" t="n">
-        <v>2914</v>
+        <v>3537</v>
       </c>
       <c r="D4" t="n">
-        <v>2946</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1021</v>
+        <v>1314</v>
       </c>
       <c r="C5" t="n">
-        <v>1164</v>
+        <v>1665</v>
       </c>
       <c r="D5" t="n">
-        <v>1313</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>271</v>
+        <v>327</v>
       </c>
       <c r="C6" t="n">
-        <v>461</v>
+        <v>407</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5858</v>
+        <v>8006</v>
       </c>
       <c r="C2" t="n">
-        <v>4939</v>
+        <v>5609</v>
       </c>
       <c r="D2" t="n">
-        <v>27707</v>
+        <v>32905</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3281</v>
+        <v>4049</v>
       </c>
       <c r="C3" t="n">
-        <v>5237</v>
+        <v>4797</v>
       </c>
       <c r="D3" t="n">
-        <v>12146</v>
+        <v>12241</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1773</v>
+        <v>2147</v>
       </c>
       <c r="C4" t="n">
-        <v>3540</v>
+        <v>3608</v>
       </c>
       <c r="D4" t="n">
-        <v>3800</v>
+        <v>4717</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>857</v>
+        <v>1121</v>
       </c>
       <c r="C5" t="n">
-        <v>1522</v>
+        <v>1916</v>
       </c>
       <c r="D5" t="n">
-        <v>1273</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>307</v>
+        <v>383</v>
       </c>
       <c r="C6" t="n">
-        <v>554</v>
+        <v>700</v>
       </c>
       <c r="D6" t="n">
-        <v>760</v>
+        <v>796</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5871,10 +5871,10 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>193</v>
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5906</v>
+        <v>6632</v>
       </c>
       <c r="C2" t="n">
-        <v>6387</v>
+        <v>5689</v>
       </c>
       <c r="D2" t="n">
-        <v>30094</v>
+        <v>28953</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3844</v>
+        <v>4986</v>
       </c>
       <c r="C3" t="n">
-        <v>4338</v>
+        <v>4530</v>
       </c>
       <c r="D3" t="n">
-        <v>13971</v>
+        <v>14811</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2206</v>
+        <v>2690</v>
       </c>
       <c r="C4" t="n">
-        <v>4509</v>
+        <v>4252</v>
       </c>
       <c r="D4" t="n">
-        <v>5447</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1181</v>
+        <v>1461</v>
       </c>
       <c r="C5" t="n">
-        <v>2691</v>
+        <v>2866</v>
       </c>
       <c r="D5" t="n">
-        <v>1743</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>540</v>
+        <v>691</v>
       </c>
       <c r="C6" t="n">
-        <v>1104</v>
+        <v>1380</v>
       </c>
       <c r="D6" t="n">
-        <v>840</v>
+        <v>919</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>184</v>
+        <v>220</v>
       </c>
       <c r="C7" t="n">
-        <v>424</v>
+        <v>498</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6266,7 +6266,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4244</v>
+        <v>5744</v>
       </c>
       <c r="C2" t="n">
-        <v>5963</v>
+        <v>4460</v>
       </c>
       <c r="D2" t="n">
-        <v>37011</v>
+        <v>27276</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3999</v>
+        <v>4766</v>
       </c>
       <c r="C3" t="n">
-        <v>4731</v>
+        <v>4468</v>
       </c>
       <c r="D3" t="n">
-        <v>15544</v>
+        <v>16007</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2614</v>
+        <v>3296</v>
       </c>
       <c r="C4" t="n">
-        <v>4316</v>
+        <v>4321</v>
       </c>
       <c r="D4" t="n">
-        <v>6865</v>
+        <v>7544</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1480</v>
+        <v>1806</v>
       </c>
       <c r="C5" t="n">
-        <v>3647</v>
+        <v>3564</v>
       </c>
       <c r="D5" t="n">
-        <v>2401</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>787</v>
+        <v>978</v>
       </c>
       <c r="C6" t="n">
-        <v>1944</v>
+        <v>2148</v>
       </c>
       <c r="D6" t="n">
-        <v>992</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>396</v>
       </c>
       <c r="C7" t="n">
-        <v>779</v>
+        <v>951</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_75_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_75_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7236</v>
+        <v>934</v>
       </c>
       <c r="C2" t="n">
-        <v>10199</v>
+        <v>4751</v>
       </c>
       <c r="D2" t="n">
-        <v>27474</v>
+        <v>12853</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4301</v>
+        <v>1401</v>
       </c>
       <c r="C3" t="n">
-        <v>3899</v>
+        <v>10278</v>
       </c>
       <c r="D3" t="n">
-        <v>16528</v>
+        <v>14094</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3399</v>
+        <v>877</v>
       </c>
       <c r="C4" t="n">
-        <v>4265</v>
+        <v>10789</v>
       </c>
       <c r="D4" t="n">
-        <v>8704</v>
+        <v>6638</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2203</v>
+        <v>445</v>
       </c>
       <c r="C5" t="n">
-        <v>3875</v>
+        <v>6232</v>
       </c>
       <c r="D5" t="n">
-        <v>3484</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1234</v>
+        <v>206</v>
       </c>
       <c r="C6" t="n">
-        <v>2818</v>
+        <v>2651</v>
       </c>
       <c r="D6" t="n">
-        <v>1358</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>593</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>1516</v>
+        <v>903</v>
       </c>
       <c r="D7" t="n">
-        <v>693</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>215</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>641</v>
+        <v>364</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8476</v>
+        <v>1004</v>
       </c>
       <c r="C2" t="n">
-        <v>9849</v>
+        <v>4349</v>
       </c>
       <c r="D2" t="n">
-        <v>31736</v>
+        <v>16509</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4593</v>
+        <v>1012</v>
       </c>
       <c r="C3" t="n">
-        <v>5951</v>
+        <v>6530</v>
       </c>
       <c r="D3" t="n">
-        <v>16905</v>
+        <v>13048</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3239</v>
+        <v>966</v>
       </c>
       <c r="C4" t="n">
-        <v>4000</v>
+        <v>10398</v>
       </c>
       <c r="D4" t="n">
-        <v>9716</v>
+        <v>7724</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2400</v>
+        <v>561</v>
       </c>
       <c r="C5" t="n">
-        <v>3936</v>
+        <v>8377</v>
       </c>
       <c r="D5" t="n">
-        <v>4146</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1500</v>
+        <v>279</v>
       </c>
       <c r="C6" t="n">
-        <v>3267</v>
+        <v>4368</v>
       </c>
       <c r="D6" t="n">
-        <v>1666</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>783</v>
+        <v>127</v>
       </c>
       <c r="C7" t="n">
-        <v>2074</v>
+        <v>1716</v>
       </c>
       <c r="D7" t="n">
-        <v>776</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>326</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1018</v>
+        <v>599</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>428</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9488</v>
+        <v>546</v>
       </c>
       <c r="C2" t="n">
-        <v>13807</v>
+        <v>1900</v>
       </c>
       <c r="D2" t="n">
-        <v>38175</v>
+        <v>11263</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5002</v>
+        <v>972</v>
       </c>
       <c r="C3" t="n">
-        <v>6766</v>
+        <v>5487</v>
       </c>
       <c r="D3" t="n">
-        <v>17602</v>
+        <v>13129</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3225</v>
+        <v>1062</v>
       </c>
       <c r="C4" t="n">
-        <v>4721</v>
+        <v>9868</v>
       </c>
       <c r="D4" t="n">
-        <v>10362</v>
+        <v>8496</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2462</v>
+        <v>564</v>
       </c>
       <c r="C5" t="n">
-        <v>3843</v>
+        <v>9942</v>
       </c>
       <c r="D5" t="n">
-        <v>4782</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1690</v>
+        <v>235</v>
       </c>
       <c r="C6" t="n">
-        <v>3513</v>
+        <v>5380</v>
       </c>
       <c r="D6" t="n">
-        <v>2001</v>
+        <v>945</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>955</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>2532</v>
+        <v>1564</v>
       </c>
       <c r="D7" t="n">
-        <v>882</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>443</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1421</v>
+        <v>510</v>
       </c>
       <c r="D8" t="n">
-        <v>501</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>169</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>653</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8710</v>
+        <v>411</v>
       </c>
       <c r="C2" t="n">
-        <v>9388</v>
+        <v>5424</v>
       </c>
       <c r="D2" t="n">
-        <v>31384</v>
+        <v>10282</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5901</v>
+        <v>676</v>
       </c>
       <c r="C3" t="n">
-        <v>10101</v>
+        <v>3334</v>
       </c>
       <c r="D3" t="n">
-        <v>19236</v>
+        <v>12083</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2274</v>
+        <v>900</v>
       </c>
       <c r="C4" t="n">
-        <v>6272</v>
+        <v>7570</v>
       </c>
       <c r="D4" t="n">
-        <v>10069</v>
+        <v>8993</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1561</v>
+        <v>687</v>
       </c>
       <c r="C5" t="n">
-        <v>3442</v>
+        <v>9795</v>
       </c>
       <c r="D5" t="n">
-        <v>3246</v>
+        <v>3749</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>882</v>
+        <v>331</v>
       </c>
       <c r="C6" t="n">
-        <v>2481</v>
+        <v>7395</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>1392</v>
+        <v>3202</v>
       </c>
       <c r="D7" t="n">
-        <v>490</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>639</v>
+        <v>927</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5407</v>
+        <v>297</v>
       </c>
       <c r="C2" t="n">
-        <v>4517</v>
+        <v>2909</v>
       </c>
       <c r="D2" t="n">
-        <v>21887</v>
+        <v>7941</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6105</v>
+        <v>513</v>
       </c>
       <c r="C3" t="n">
-        <v>8872</v>
+        <v>3843</v>
       </c>
       <c r="D3" t="n">
-        <v>19780</v>
+        <v>11175</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3162</v>
+        <v>759</v>
       </c>
       <c r="C4" t="n">
-        <v>8086</v>
+        <v>5800</v>
       </c>
       <c r="D4" t="n">
-        <v>11364</v>
+        <v>9337</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1739</v>
+        <v>731</v>
       </c>
       <c r="C5" t="n">
-        <v>4703</v>
+        <v>9112</v>
       </c>
       <c r="D5" t="n">
-        <v>4061</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1044</v>
+        <v>401</v>
       </c>
       <c r="C6" t="n">
-        <v>2964</v>
+        <v>8487</v>
       </c>
       <c r="D6" t="n">
-        <v>1107</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>385</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>1788</v>
+        <v>4529</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>862</v>
+        <v>1428</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>409</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5160</v>
+        <v>627</v>
       </c>
       <c r="C2" t="n">
-        <v>8125</v>
+        <v>7153</v>
       </c>
       <c r="D2" t="n">
-        <v>27219</v>
+        <v>11504</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4928</v>
+        <v>363</v>
       </c>
       <c r="C3" t="n">
-        <v>6052</v>
+        <v>3049</v>
       </c>
       <c r="D3" t="n">
-        <v>18737</v>
+        <v>10027</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3775</v>
+        <v>579</v>
       </c>
       <c r="C4" t="n">
-        <v>8302</v>
+        <v>4796</v>
       </c>
       <c r="D4" t="n">
-        <v>12392</v>
+        <v>9335</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2079</v>
+        <v>685</v>
       </c>
       <c r="C5" t="n">
-        <v>6196</v>
+        <v>7491</v>
       </c>
       <c r="D5" t="n">
-        <v>5059</v>
+        <v>4873</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1234</v>
+        <v>482</v>
       </c>
       <c r="C6" t="n">
-        <v>3748</v>
+        <v>8751</v>
       </c>
       <c r="D6" t="n">
-        <v>1517</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>561</v>
+        <v>188</v>
       </c>
       <c r="C7" t="n">
-        <v>2311</v>
+        <v>6078</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>759</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1242</v>
+        <v>2596</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>535</v>
+        <v>762</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3093</v>
+        <v>436</v>
       </c>
       <c r="C2" t="n">
-        <v>3827</v>
+        <v>3948</v>
       </c>
       <c r="D2" t="n">
-        <v>18988</v>
+        <v>8466</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4849</v>
+        <v>552</v>
       </c>
       <c r="C3" t="n">
-        <v>6564</v>
+        <v>4320</v>
       </c>
       <c r="D3" t="n">
-        <v>19199</v>
+        <v>10899</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4146</v>
+        <v>917</v>
       </c>
       <c r="C4" t="n">
-        <v>8191</v>
+        <v>7142</v>
       </c>
       <c r="D4" t="n">
-        <v>13206</v>
+        <v>9546</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2175</v>
+        <v>477</v>
       </c>
       <c r="C5" t="n">
-        <v>7624</v>
+        <v>11723</v>
       </c>
       <c r="D5" t="n">
-        <v>5328</v>
+        <v>4458</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1020</v>
+        <v>173</v>
       </c>
       <c r="C6" t="n">
-        <v>4497</v>
+        <v>7843</v>
       </c>
       <c r="D6" t="n">
-        <v>1472</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>58</v>
       </c>
       <c r="C7" t="n">
-        <v>2357</v>
+        <v>2544</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>901</v>
+        <v>746</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4482</v>
+        <v>229</v>
       </c>
       <c r="C2" t="n">
-        <v>8143</v>
+        <v>2942</v>
       </c>
       <c r="D2" t="n">
-        <v>16803</v>
+        <v>6548</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3534</v>
+        <v>425</v>
       </c>
       <c r="C3" t="n">
-        <v>4744</v>
+        <v>3670</v>
       </c>
       <c r="D3" t="n">
-        <v>18064</v>
+        <v>9802</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3907</v>
+        <v>628</v>
       </c>
       <c r="C4" t="n">
-        <v>7333</v>
+        <v>5409</v>
       </c>
       <c r="D4" t="n">
-        <v>13725</v>
+        <v>9086</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2623</v>
+        <v>461</v>
       </c>
       <c r="C5" t="n">
-        <v>7788</v>
+        <v>8567</v>
       </c>
       <c r="D5" t="n">
-        <v>6300</v>
+        <v>4589</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1311</v>
+        <v>166</v>
       </c>
       <c r="C6" t="n">
-        <v>5791</v>
+        <v>7718</v>
       </c>
       <c r="D6" t="n">
-        <v>1971</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>384</v>
+        <v>45</v>
       </c>
       <c r="C7" t="n">
-        <v>3218</v>
+        <v>3382</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1455</v>
+        <v>879</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>461</v>
+        <v>261</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>118</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3168</v>
+        <v>228</v>
       </c>
       <c r="C2" t="n">
-        <v>4898</v>
+        <v>11723</v>
       </c>
       <c r="D2" t="n">
-        <v>12855</v>
+        <v>9516</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3362</v>
+        <v>281</v>
       </c>
       <c r="C3" t="n">
-        <v>5507</v>
+        <v>2868</v>
       </c>
       <c r="D3" t="n">
-        <v>17103</v>
+        <v>8617</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3499</v>
+        <v>471</v>
       </c>
       <c r="C4" t="n">
-        <v>6347</v>
+        <v>4361</v>
       </c>
       <c r="D4" t="n">
-        <v>13981</v>
+        <v>8940</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2865</v>
+        <v>485</v>
       </c>
       <c r="C5" t="n">
-        <v>7763</v>
+        <v>6833</v>
       </c>
       <c r="D5" t="n">
-        <v>6953</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1530</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>6630</v>
+        <v>8051</v>
       </c>
       <c r="D6" t="n">
-        <v>2379</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>346</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>4042</v>
+        <v>5495</v>
       </c>
       <c r="D7" t="n">
-        <v>800</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1864</v>
+        <v>2015</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3920</v>
+        <v>204</v>
       </c>
       <c r="C2" t="n">
-        <v>11431</v>
+        <v>11965</v>
       </c>
       <c r="D2" t="n">
-        <v>13117</v>
+        <v>8244</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2774</v>
+        <v>215</v>
       </c>
       <c r="C3" t="n">
-        <v>4737</v>
+        <v>6132</v>
       </c>
       <c r="D3" t="n">
-        <v>15498</v>
+        <v>8160</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2999</v>
+        <v>341</v>
       </c>
       <c r="C4" t="n">
-        <v>5807</v>
+        <v>3539</v>
       </c>
       <c r="D4" t="n">
-        <v>14005</v>
+        <v>8529</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2836</v>
+        <v>433</v>
       </c>
       <c r="C5" t="n">
-        <v>7030</v>
+        <v>5528</v>
       </c>
       <c r="D5" t="n">
-        <v>7686</v>
+        <v>5673</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1812</v>
+        <v>329</v>
       </c>
       <c r="C6" t="n">
-        <v>7074</v>
+        <v>7422</v>
       </c>
       <c r="D6" t="n">
-        <v>2919</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>635</v>
+        <v>141</v>
       </c>
       <c r="C7" t="n">
-        <v>4978</v>
+        <v>6566</v>
       </c>
       <c r="D7" t="n">
-        <v>977</v>
+        <v>909</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>2610</v>
+        <v>3514</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>966</v>
+        <v>1136</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7435</v>
+        <v>3000</v>
       </c>
       <c r="C2" t="n">
-        <v>2493</v>
+        <v>16294</v>
       </c>
       <c r="D2" t="n">
-        <v>16429</v>
+        <v>12629</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2839</v>
+        <v>635</v>
       </c>
       <c r="C2" t="n">
-        <v>6584</v>
+        <v>29425</v>
       </c>
       <c r="D2" t="n">
-        <v>9759</v>
+        <v>10215</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3648</v>
+        <v>175</v>
       </c>
       <c r="C3" t="n">
-        <v>6653</v>
+        <v>7581</v>
       </c>
       <c r="D3" t="n">
-        <v>16553</v>
+        <v>7635</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4152</v>
+        <v>252</v>
       </c>
       <c r="C4" t="n">
-        <v>8256</v>
+        <v>4610</v>
       </c>
       <c r="D4" t="n">
-        <v>14348</v>
+        <v>8213</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1726</v>
+        <v>367</v>
       </c>
       <c r="C5" t="n">
-        <v>10137</v>
+        <v>4519</v>
       </c>
       <c r="D5" t="n">
-        <v>6964</v>
+        <v>5911</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>586</v>
+        <v>340</v>
       </c>
       <c r="C6" t="n">
-        <v>6195</v>
+        <v>6573</v>
       </c>
       <c r="D6" t="n">
-        <v>2263</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>116</v>
+        <v>191</v>
       </c>
       <c r="C7" t="n">
-        <v>2557</v>
+        <v>6842</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>946</v>
+        <v>4708</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>2021</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>598</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8125</v>
+        <v>3174</v>
       </c>
       <c r="C2" t="n">
-        <v>7814</v>
+        <v>12886</v>
       </c>
       <c r="D2" t="n">
-        <v>24844</v>
+        <v>21859</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3158</v>
+        <v>970</v>
       </c>
       <c r="C3" t="n">
-        <v>1256</v>
+        <v>6434</v>
       </c>
       <c r="D3" t="n">
-        <v>3399</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6330</v>
+        <v>2029</v>
       </c>
       <c r="C2" t="n">
-        <v>5588</v>
+        <v>5745</v>
       </c>
       <c r="D2" t="n">
-        <v>30724</v>
+        <v>24079</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4633</v>
+        <v>1751</v>
       </c>
       <c r="C3" t="n">
-        <v>4283</v>
+        <v>8821</v>
       </c>
       <c r="D3" t="n">
-        <v>6751</v>
+        <v>5597</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1406</v>
+        <v>475</v>
       </c>
       <c r="C4" t="n">
-        <v>781</v>
+        <v>4001</v>
       </c>
       <c r="D4" t="n">
-        <v>1866</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5235</v>
+        <v>1394</v>
       </c>
       <c r="C2" t="n">
-        <v>7334</v>
+        <v>7150</v>
       </c>
       <c r="D2" t="n">
-        <v>29635</v>
+        <v>28480</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4494</v>
+        <v>1558</v>
       </c>
       <c r="C3" t="n">
-        <v>4323</v>
+        <v>6152</v>
       </c>
       <c r="D3" t="n">
-        <v>10100</v>
+        <v>8290</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2569</v>
+        <v>967</v>
       </c>
       <c r="C4" t="n">
-        <v>2748</v>
+        <v>6740</v>
       </c>
       <c r="D4" t="n">
-        <v>2747</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>625</v>
+        <v>246</v>
       </c>
       <c r="C5" t="n">
-        <v>523</v>
+        <v>2350</v>
       </c>
       <c r="D5" t="n">
-        <v>1271</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7266</v>
+        <v>1459</v>
       </c>
       <c r="C2" t="n">
-        <v>6570</v>
+        <v>8850</v>
       </c>
       <c r="D2" t="n">
-        <v>22373</v>
+        <v>26634</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3994</v>
+        <v>1225</v>
       </c>
       <c r="C3" t="n">
-        <v>5111</v>
+        <v>5798</v>
       </c>
       <c r="D3" t="n">
-        <v>12358</v>
+        <v>10923</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2965</v>
+        <v>1073</v>
       </c>
       <c r="C4" t="n">
-        <v>3537</v>
+        <v>6272</v>
       </c>
       <c r="D4" t="n">
-        <v>4004</v>
+        <v>3418</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1314</v>
+        <v>512</v>
       </c>
       <c r="C5" t="n">
-        <v>1665</v>
+        <v>4661</v>
       </c>
       <c r="D5" t="n">
-        <v>1475</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>327</v>
+        <v>161</v>
       </c>
       <c r="C6" t="n">
-        <v>407</v>
+        <v>1341</v>
       </c>
       <c r="D6" t="n">
-        <v>958</v>
+        <v>823</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>292</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8006</v>
+        <v>1537</v>
       </c>
       <c r="C2" t="n">
-        <v>5609</v>
+        <v>12025</v>
       </c>
       <c r="D2" t="n">
-        <v>32905</v>
+        <v>22464</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4049</v>
+        <v>1099</v>
       </c>
       <c r="C3" t="n">
-        <v>4797</v>
+        <v>6398</v>
       </c>
       <c r="D3" t="n">
-        <v>12241</v>
+        <v>12646</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2147</v>
+        <v>981</v>
       </c>
       <c r="C4" t="n">
-        <v>3608</v>
+        <v>5891</v>
       </c>
       <c r="D4" t="n">
-        <v>4717</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1121</v>
+        <v>676</v>
       </c>
       <c r="C5" t="n">
-        <v>1916</v>
+        <v>5383</v>
       </c>
       <c r="D5" t="n">
-        <v>1500</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>383</v>
+        <v>286</v>
       </c>
       <c r="C6" t="n">
-        <v>700</v>
+        <v>2952</v>
       </c>
       <c r="D6" t="n">
-        <v>796</v>
+        <v>883</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>243</v>
+        <v>795</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>296</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6632</v>
+        <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>5689</v>
+        <v>16302</v>
       </c>
       <c r="D2" t="n">
-        <v>28953</v>
+        <v>23771</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4986</v>
+        <v>1059</v>
       </c>
       <c r="C3" t="n">
-        <v>4530</v>
+        <v>7915</v>
       </c>
       <c r="D3" t="n">
-        <v>14811</v>
+        <v>13131</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2690</v>
+        <v>886</v>
       </c>
       <c r="C4" t="n">
-        <v>4252</v>
+        <v>6016</v>
       </c>
       <c r="D4" t="n">
-        <v>6045</v>
+        <v>5711</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1461</v>
+        <v>723</v>
       </c>
       <c r="C5" t="n">
-        <v>2866</v>
+        <v>5509</v>
       </c>
       <c r="D5" t="n">
-        <v>2102</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>691</v>
+        <v>407</v>
       </c>
       <c r="C6" t="n">
-        <v>1380</v>
+        <v>3991</v>
       </c>
       <c r="D6" t="n">
-        <v>919</v>
+        <v>977</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>498</v>
+        <v>1767</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>230</v>
+        <v>508</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5744</v>
+        <v>1786</v>
       </c>
       <c r="C2" t="n">
-        <v>4460</v>
+        <v>10433</v>
       </c>
       <c r="D2" t="n">
-        <v>27276</v>
+        <v>19014</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4766</v>
+        <v>1467</v>
       </c>
       <c r="C3" t="n">
-        <v>4468</v>
+        <v>12343</v>
       </c>
       <c r="D3" t="n">
-        <v>16007</v>
+        <v>14252</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3296</v>
+        <v>668</v>
       </c>
       <c r="C4" t="n">
-        <v>4321</v>
+        <v>8927</v>
       </c>
       <c r="D4" t="n">
-        <v>7544</v>
+        <v>5224</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1806</v>
+        <v>376</v>
       </c>
       <c r="C5" t="n">
-        <v>3564</v>
+        <v>3911</v>
       </c>
       <c r="D5" t="n">
-        <v>2737</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>978</v>
+        <v>157</v>
       </c>
       <c r="C6" t="n">
-        <v>2148</v>
+        <v>1731</v>
       </c>
       <c r="D6" t="n">
-        <v>1121</v>
+        <v>638</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>396</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>951</v>
+        <v>497</v>
       </c>
       <c r="D7" t="n">
-        <v>615</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>366</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
